--- a/templates/01_每日收益日报.xlsx
+++ b/templates/01_每日收益日报.xlsx
@@ -1392,7 +1392,7 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>杭州滨江云璟酒店 · 320 间房 · 中高端全服务 ｜ 酒店收益管理学院 HRMA ｜ 口径以 SPEC.md 为准</t>
+          <t>杭州滨江云璟酒店 · 320 间房 · 中高端全服务 ｜ RMC收益管理社区 ｜ 口径以 SPEC.md 为准</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>TrevPAR</t>
+          <t>TRevPAR</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>全服务酒店须同时看（等价 RevPE）</t>
+          <t>全服务酒店须同时看</t>
         </is>
       </c>
     </row>
